--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,12 +20,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
   <si>
     <t xml:space="preserve">고유 ID</t>
   </si>
   <si>
     <t xml:space="preserve">설명</t>
+  </si>
+  <si>
+    <t xml:space="preserve">회복량</t>
   </si>
   <si>
     <t xml:space="preserve">(name)</t>
@@ -55,66 +58,31 @@
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
-    <t xml:space="preserve">Item_DummyBox_1</t>
+    <t xml:space="preserve">EffectValue</t>
   </si>
   <si>
-    <t xml:space="preserve">상자</t>
+    <t xml:space="preserve">Obj_Carrot_01</t>
   </si>
   <si>
-    <t xml:space="preserve">상자다. 딱히 의미가 있진 않다.</t>
+    <t xml:space="preserve">당근</t>
+  </si>
+  <si>
+    <t xml:space="preserve">필드 당근</t>
   </si>
   <si>
     <t xml:space="preserve">Normal</t>
   </si>
   <si>
-    <t xml:space="preserve">Icon/Icon_Item_Box_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_Gold_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">화폐</t>
-  </si>
-  <si>
-    <t xml:space="preserve">지역에 나타나는 금화</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon/Icon_Item_Gold_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">의문의 모자</t>
-  </si>
-  <si>
-    <t xml:space="preserve">착용하면 공격력이 강해진다.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon/Icon_Item_Equip_Hat_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Item_Corn_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">옥수수</t>
-  </si>
-  <si>
-    <t xml:space="preserve">옥수수다</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Icon/Icon_Item_Corn</t>
+    <t xml:space="preserve">Icon/Icon_Item_Carrot_01</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -225,32 +193,40 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -508,7 +484,7 @@
   <sheetFormatPr defaultColWidth="12.68359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.73"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="51.17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.81"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.68"/>
@@ -525,353 +501,328 @@
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>3</v>
+      <c r="G2" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="3" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="L3" s="0"/>
-      <c r="M3" s="0"/>
-      <c r="N3" s="0"/>
-      <c r="O3" s="0"/>
+        <v>11</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>11</v>
+      <c r="A4" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="8" t="n">
         <v>20</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="6"/>
+      <c r="F4" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="6"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="6"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-      <c r="J8" s="6"/>
-      <c r="K8" s="6"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="6"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
-      <c r="K10" s="6"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
-      <c r="K11" s="6"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
-      <c r="K14" s="6"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6"/>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="6"/>
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6"/>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6"/>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="8"/>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6"/>
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
-    <t xml:space="preserve">고유 ID</t>
+    <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
   <si>
-    <t xml:space="preserve">설명</t>
-  </si>
-  <si>
-    <t xml:space="preserve">회복량</t>
+    <t xml:space="preserve">우선 프리팹으로 구현하자!</t>
   </si>
   <si>
     <t xml:space="preserve">(name)</t>
@@ -43,37 +40,37 @@
     <t xml:space="preserve">Id</t>
   </si>
   <si>
+    <t xml:space="preserve">FieldObjectType</t>
+  </si>
+  <si>
     <t xml:space="preserve">Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ItemType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MaxStackCount</t>
+    <t xml:space="preserve">HealValue</t>
   </si>
   <si>
     <t xml:space="preserve">IconPath</t>
   </si>
   <si>
-    <t xml:space="preserve">EffectValue</t>
+    <t xml:space="preserve">PrefabPath</t>
   </si>
   <si>
-    <t xml:space="preserve">Obj_Carrot_01</t>
+    <t xml:space="preserve">obj_cherry_01</t>
   </si>
   <si>
-    <t xml:space="preserve">당근</t>
+    <t xml:space="preserve">Heal</t>
   </si>
   <si>
-    <t xml:space="preserve">필드 당근</t>
+    <t xml:space="preserve">체리</t>
   </si>
   <si>
-    <t xml:space="preserve">Normal</t>
+    <t xml:space="preserve">30</t>
   </si>
   <si>
-    <t xml:space="preserve">Icon/Icon_Item_Carrot_01</t>
+    <t xml:space="preserve">Icon/Icon_Obj/Icon_Item/Icon_Item_Cherry_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prefab/Obj/Item/DropItem_Cherry</t>
   </si>
 </sst>
 </file>
@@ -84,7 +81,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -118,6 +115,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
@@ -130,6 +134,13 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="4">
@@ -193,7 +204,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -202,19 +213,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -222,12 +249,16 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -480,350 +511,393 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O1000"/>
-  <sheetFormatPr defaultColWidth="12.68359375" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:R999"/>
+  <sheetFormatPr defaultColWidth="12.65625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="51.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="26.81"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="28.68"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="7" style="1" width="12.68"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16" style="1" width="12.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="19.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="51.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="51.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="8" style="1" width="12.65"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="19" style="1" width="12.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" s="5" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="8"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="C4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="E4" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="F4" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G4" s="8" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="12"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
+      <c r="A5" s="13"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="12"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="12"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="12"/>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="12"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="12"/>
+      <c r="N8" s="12"/>
+      <c r="O8" s="12"/>
+      <c r="P8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
+      <c r="A9" s="3"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
+      <c r="A10" s="3"/>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="12"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="12"/>
+      <c r="P11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="8"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="8"/>
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
     </row>
     <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="8"/>
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
     </row>
     <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="F24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="F25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="F26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="F27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8"/>
-      <c r="B28" s="8"/>
-      <c r="C28" s="8"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8"/>
-      <c r="B30" s="8"/>
-      <c r="C30" s="8"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8"/>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-    </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-    </row>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+    </row>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1788,10 +1862,9 @@
     <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
   <si>
-    <t xml:space="preserve">우선 프리팹으로 구현하자!</t>
+    <t xml:space="preserve">프리펩 경로 (=어드레서블 네임)</t>
   </si>
   <si>
     <t xml:space="preserve">(name)</t>
@@ -49,9 +49,6 @@
     <t xml:space="preserve">HealValue</t>
   </si>
   <si>
-    <t xml:space="preserve">IconPath</t>
-  </si>
-  <si>
     <t xml:space="preserve">PrefabPath</t>
   </si>
   <si>
@@ -67,10 +64,19 @@
     <t xml:space="preserve">30</t>
   </si>
   <si>
-    <t xml:space="preserve">Icon/Icon_Obj/Icon_Item/Icon_Item_Cherry_01</t>
+    <t xml:space="preserve">Item/DropItem_Cherry</t>
   </si>
   <si>
-    <t xml:space="preserve">Prefab/Obj/Item/DropItem_Cherry</t>
+    <t xml:space="preserve">obj_collecton_gem_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_01</t>
   </si>
 </sst>
 </file>
@@ -511,17 +517,17 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R999"/>
+  <dimension ref="A1:XFB999"/>
   <sheetFormatPr defaultColWidth="12.65625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="19.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="51.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="51.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45.92"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.78"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16" min="8" style="1" width="12.65"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="19" style="1" width="12.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="45.92"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.78"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="7" style="1" width="12.65"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="18" style="1" width="12.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="0" width="11.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.64"/>
   </cols>
   <sheetData>
@@ -532,8 +538,7 @@
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
       <c r="D1" s="4"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
     </row>
@@ -553,10 +558,7 @@
       <c r="E2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="3" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
@@ -574,33 +576,29 @@
       <c r="E3" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
+      <c r="XFB3" s="0"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
       <c r="J4" s="12"/>
@@ -609,14 +607,21 @@
       <c r="M4" s="12"/>
       <c r="N4" s="12"/>
       <c r="O4" s="12"/>
-      <c r="P4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+      <c r="A5" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="D5" s="13"/>
-      <c r="E5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>18</v>
+      </c>
       <c r="F5" s="12"/>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
@@ -627,7 +632,6 @@
       <c r="M5" s="12"/>
       <c r="N5" s="12"/>
       <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3"/>
@@ -645,7 +649,6 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
-      <c r="P6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3"/>
@@ -663,7 +666,6 @@
       <c r="M7" s="12"/>
       <c r="N7" s="12"/>
       <c r="O7" s="12"/>
-      <c r="P7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3"/>
@@ -681,7 +683,6 @@
       <c r="M8" s="12"/>
       <c r="N8" s="12"/>
       <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="3"/>
@@ -699,7 +700,6 @@
       <c r="M9" s="12"/>
       <c r="N9" s="12"/>
       <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3"/>
@@ -717,7 +717,6 @@
       <c r="M10" s="12"/>
       <c r="N10" s="12"/>
       <c r="O10" s="12"/>
-      <c r="P10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
@@ -735,7 +734,6 @@
       <c r="M11" s="12"/>
       <c r="N11" s="12"/>
       <c r="O11" s="12"/>
-      <c r="P11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
@@ -753,7 +751,6 @@
       <c r="M12" s="12"/>
       <c r="N12" s="12"/>
       <c r="O12" s="12"/>
-      <c r="P12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
@@ -771,7 +768,6 @@
       <c r="M13" s="12"/>
       <c r="N13" s="12"/>
       <c r="O13" s="12"/>
-      <c r="P13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
@@ -789,7 +785,6 @@
       <c r="M14" s="12"/>
       <c r="N14" s="12"/>
       <c r="O14" s="12"/>
-      <c r="P14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12"/>
@@ -811,7 +806,6 @@
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
       <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
@@ -842,25 +836,25 @@
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="E24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="E25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="E26" s="12"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="E27" s="12"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -52,6 +52,9 @@
     <t xml:space="preserve">PrefabPath</t>
   </si>
   <si>
+    <t xml:space="preserve">CollectionId</t>
+  </si>
+  <si>
     <t xml:space="preserve">obj_cherry_01</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
   </si>
   <si>
     <t xml:space="preserve">Collective/obj_collecton_gem_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_01</t>
   </si>
 </sst>
 </file>
@@ -223,6 +229,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -249,10 +259,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -527,77 +533,81 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.78"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="15" min="7" style="1" width="12.65"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16381" min="18" style="1" width="12.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="0" width="11.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="3" width="11.64"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="6" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="3"/>
-    </row>
-    <row r="3" s="9" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="F2" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" s="10" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="XFB3" s="0"/>
+      <c r="F3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="XFB3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="4" t="s">
         <v>13</v>
       </c>
+      <c r="D4" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="E4" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="F4" s="4"/>
       <c r="G4" s="12"/>
       <c r="H4" s="12"/>
       <c r="I4" s="12"/>
@@ -610,19 +620,21 @@
     </row>
     <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="12"/>
+        <v>19</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="G5" s="12"/>
       <c r="H5" s="12"/>
       <c r="I5" s="12"/>
@@ -634,10 +646,10 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="4"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
@@ -651,10 +663,10 @@
       <c r="O6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="12"/>
@@ -668,10 +680,10 @@
       <c r="O7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="12"/>
@@ -685,10 +697,10 @@
       <c r="O8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
@@ -702,10 +714,10 @@
       <c r="O9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="12"/>
@@ -719,10 +731,10 @@
       <c r="O10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
       <c r="E11" s="12"/>
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
@@ -736,10 +748,10 @@
       <c r="O11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
       <c r="E12" s="12"/>
       <c r="F12" s="12"/>
       <c r="G12" s="12"/>
@@ -753,10 +765,10 @@
       <c r="O12" s="12"/>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
       <c r="E13" s="12"/>
       <c r="F13" s="12"/>
       <c r="G13" s="12"/>
@@ -770,10 +782,10 @@
       <c r="O13" s="12"/>
     </row>
     <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="4"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
       <c r="E14" s="12"/>
       <c r="F14" s="12"/>
       <c r="G14" s="12"/>

--- a/JsonConverter/ExcelFiles/Item.xlsx
+++ b/JsonConverter/ExcelFiles/Item.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t xml:space="preserve">캐릭터 고유 ID</t>
   </si>
@@ -70,19 +70,82 @@
     <t xml:space="preserve">Item/DropItem_Cherry</t>
   </si>
   <si>
+    <t xml:space="preserve">obj_collecton_gem_00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective</t>
+  </si>
+  <si>
+    <t xml:space="preserve">보석</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_00</t>
+  </si>
+  <si>
     <t xml:space="preserve">obj_collecton_gem_01</t>
   </si>
   <si>
-    <t xml:space="preserve">Collective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">보석</t>
-  </si>
-  <si>
     <t xml:space="preserve">Collective/obj_collecton_gem_01</t>
   </si>
   <si>
     <t xml:space="preserve">collection_gem_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obj_collecton_gem_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obj_collecton_gem_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obj_collecton_gem_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obj_collecton_gem_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obj_collecton_gem_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obj_collecton_gem_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collective/obj_collecton_gem_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">collection_gem_07</t>
   </si>
 </sst>
 </file>
@@ -93,7 +156,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -152,6 +215,13 @@
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
       <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
+      <family val="0"/>
       <charset val="129"/>
     </font>
   </fonts>
@@ -216,7 +286,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -270,6 +340,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -523,7 +597,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFB999"/>
+  <dimension ref="A1:XFB1000"/>
   <sheetFormatPr defaultColWidth="12.65625" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="19.63"/>
@@ -646,12 +720,22 @@
       <c r="O5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
+      <c r="A6" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
@@ -663,12 +747,22 @@
       <c r="O6" s="12"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
+      <c r="A7" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D7" s="5"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>26</v>
+      </c>
       <c r="G7" s="12"/>
       <c r="H7" s="12"/>
       <c r="I7" s="12"/>
@@ -680,12 +774,22 @@
       <c r="O7" s="12"/>
     </row>
     <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
+      <c r="A8" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D8" s="5"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>29</v>
+      </c>
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
@@ -697,12 +801,22 @@
       <c r="O8" s="12"/>
     </row>
     <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
+      <c r="A9" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D9" s="5"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
+      <c r="E9" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>32</v>
+      </c>
       <c r="G9" s="12"/>
       <c r="H9" s="12"/>
       <c r="I9" s="12"/>
@@ -714,12 +828,22 @@
       <c r="O9" s="12"/>
     </row>
     <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
+      <c r="A10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D10" s="5"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>35</v>
+      </c>
       <c r="G10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
@@ -731,12 +855,22 @@
       <c r="O10" s="12"/>
     </row>
     <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
+      <c r="A11" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D11" s="5"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
+      <c r="E11" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>38</v>
+      </c>
       <c r="G11" s="12"/>
       <c r="H11" s="12"/>
       <c r="I11" s="12"/>
@@ -748,12 +882,22 @@
       <c r="O11" s="12"/>
     </row>
     <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
+      <c r="A12" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>18</v>
+      </c>
       <c r="D12" s="5"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
+      <c r="E12" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>41</v>
+      </c>
       <c r="G12" s="12"/>
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
@@ -799,9 +943,21 @@
       <c r="O14" s="12"/>
     </row>
     <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12"/>
@@ -817,12 +973,12 @@
       <c r="A18" s="12"/>
       <c r="B18" s="12"/>
       <c r="C18" s="12"/>
-      <c r="E18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12"/>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
+      <c r="E19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12"/>
@@ -848,7 +1004,6 @@
       <c r="A24" s="12"/>
       <c r="B24" s="12"/>
       <c r="C24" s="12"/>
-      <c r="E24" s="12"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12"/>
@@ -872,6 +1027,7 @@
       <c r="A28" s="12"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
+      <c r="E28" s="12"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12"/>
@@ -903,7 +1059,11 @@
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+    </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -1868,6 +2028,7 @@
     <row r="997" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="998" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="999" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1000" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
